--- a/public/assets/sample_excels/order_detail_import.xlsx
+++ b/public/assets/sample_excels/order_detail_import.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Anand\auromics\public\assets\sample_excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB38898A-92F2-4FBE-ACEC-B740C2D1FB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="11760" tabRatio="500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -28,16 +34,43 @@
     <t>Customer  ID</t>
   </si>
   <si>
-    <t>04.03.2024</t>
-  </si>
-  <si>
-    <t>001</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Product Size</t>
+  </si>
+  <si>
+    <t>Product Model</t>
+  </si>
+  <si>
+    <t>Product color</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Available quantity</t>
+  </si>
+  <si>
+    <t>Delivery Date</t>
+  </si>
+  <si>
+    <t>Order Status</t>
+  </si>
+  <si>
+    <t>Total Raw Material</t>
+  </si>
+  <si>
+    <t>Weight per item</t>
+  </si>
+  <si>
+    <t>Available weight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -70,10 +103,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -84,14 +117,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -129,7 +165,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -163,6 +199,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -197,9 +234,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -372,16 +410,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -394,19 +440,79 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:14">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
+      <c r="C2" s="3">
+        <v>45664</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3">
+        <v>45671</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
